--- a/business_surveys/009_data_collection_survey--business_surveys.xlsx
+++ b/business_surveys/009_data_collection_survey--business_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'business'}</t>
+          <t>business</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Business'}</t>
+          <t>Business</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'feedback'}</t>
+          <t>feedback</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Feedback'}</t>
+          <t>Feedback</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'marketing'}</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Marketing'}</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'sales'}</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Sales'}</t>
+          <t>Sales</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'support'}</t>
+          <t>support</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Support'}</t>
+          <t>Support</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'approved'}</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Approved'}</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'rejected'}</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Rejected'}</t>
+          <t>Rejected</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Spanish'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'french'}</t>
+          <t>french</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'French'}</t>
+          <t>French</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'high_school_diploma'}</t>
+          <t>high_school_diploma</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'High School Diploma'}</t>
+          <t>High School Diploma</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'college'}</t>
+          <t>college</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'College'}</t>
+          <t>College</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'university'}</t>
+          <t>university</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'University'}</t>
+          <t>University</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'usa'}</t>
+          <t>usa</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'USA'}</t>
+          <t>USA</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'canada'}</t>
+          <t>canada</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Canada'}</t>
+          <t>Canada</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'uk'}</t>
+          <t>uk</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'UK'}</t>
+          <t>UK</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'reading'}</t>
+          <t>reading</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'Reading'}</t>
+          <t>Reading</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'sports'}</t>
+          <t>sports</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'Sports'}</t>
+          <t>Sports</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'traveling'}</t>
+          <t>traveling</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'Traveling'}</t>
+          <t>Traveling</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'male'}</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'Male'}</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'female'}</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'Female'}</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
